--- a/docs/d/116/inyear.xlsx
+++ b/docs/d/116/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="P3" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="9" t="n">
         <v>1</v>
@@ -4073,7 +4073,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" s="10" t="n">
         <v>1</v>
@@ -4532,7 +4532,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4575,8 +4575,8 @@
       <c r="P38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q38" s="9" t="n">
-        <v>1</v>
+      <c r="Q38" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R38" s="9" t="n">
         <v>0</v>
@@ -4883,7 +4883,7 @@
         <v>2</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" s="9" t="n">
         <v>0</v>
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14868,8 +14868,8 @@
       <c r="S138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T138" s="9" t="n">
-        <v>0</v>
+      <c r="T138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U138" s="9" t="n">
         <v>0</v>
@@ -15350,7 +15350,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -16109,7 +16109,7 @@
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>

--- a/docs/d/116/inyear.xlsx
+++ b/docs/d/116/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,11 @@
       <c r="AB3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -2373,7 +2377,11 @@
       <c r="AB16" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC16" s="4" t="inlineStr"/>
+      <c r="AC16" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2579,7 +2587,11 @@
       <c r="AB18" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC18" s="4" t="inlineStr"/>
+      <c r="AC18" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -2680,7 +2692,11 @@
       <c r="AB19" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC19" s="4" t="inlineStr"/>
+      <c r="AC19" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2781,7 +2797,11 @@
       <c r="AB20" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC20" s="4" t="inlineStr"/>
+      <c r="AC20" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2882,7 +2902,11 @@
       <c r="AB21" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC21" s="4" t="inlineStr"/>
+      <c r="AC21" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -3189,7 +3213,11 @@
       <c r="AB24" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC24" s="4" t="inlineStr"/>
+      <c r="AC24" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -3496,7 +3524,11 @@
       <c r="AB27" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC27" s="4" t="inlineStr"/>
+      <c r="AC27" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -4102,7 +4134,11 @@
       <c r="AB33" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC33" s="4" t="inlineStr"/>
+      <c r="AC33" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -4611,7 +4647,11 @@
       <c r="AB38" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC38" s="4" t="inlineStr"/>
+      <c r="AC38" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -6352,7 +6392,11 @@
       <c r="AB55" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC55" s="4" t="inlineStr"/>
+      <c r="AC55" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -6558,7 +6602,11 @@
       <c r="AB57" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC57" s="4" t="inlineStr"/>
+      <c r="AC57" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -6865,7 +6913,11 @@
       <c r="AB60" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC60" s="4" t="inlineStr"/>
+      <c r="AC60" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -7176,7 +7228,11 @@
       <c r="AB63" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC63" s="4" t="inlineStr"/>
+      <c r="AC63" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -7378,7 +7434,11 @@
       <c r="AB65" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC65" s="4" t="inlineStr"/>
+      <c r="AC65" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -8521,7 +8581,11 @@
       <c r="AB76" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC76" s="4" t="inlineStr"/>
+      <c r="AC76" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -8828,7 +8892,11 @@
       <c r="AB79" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC79" s="4" t="inlineStr"/>
+      <c r="AC79" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -9349,7 +9417,11 @@
       <c r="AB84" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC84" s="4" t="inlineStr"/>
+      <c r="AC84" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -9967,7 +10039,11 @@
       <c r="AB90" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC90" s="4" t="inlineStr"/>
+      <c r="AC90" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -10589,7 +10665,11 @@
       <c r="AB96" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC96" s="4" t="inlineStr"/>
+      <c r="AC96" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -11409,7 +11489,11 @@
       <c r="AB104" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC104" s="4" t="inlineStr"/>
+      <c r="AC104" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -12136,7 +12220,11 @@
       <c r="AB111" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC111" s="4" t="inlineStr"/>
+      <c r="AC111" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -12548,7 +12636,11 @@
       <c r="AB115" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC115" s="4" t="inlineStr"/>
+      <c r="AC115" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -14386,7 +14478,11 @@
       <c r="AB133" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC133" s="4" t="inlineStr"/>
+      <c r="AC133" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">

--- a/docs/d/116/inyear.xlsx
+++ b/docs/d/116/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 84 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 84 clubs short</t>
         </is>
       </c>
     </row>
@@ -2837,13 +2837,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -4104,8 +4104,8 @@
       <c r="R33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S33" s="9" t="n">
-        <v>1</v>
+      <c r="S33" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T33" s="10" t="n">
         <v>1</v>
@@ -7684,13 +7684,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>4</v>
       </c>
       <c r="W68" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X68" s="10" t="n">
         <v>7</v>
@@ -9974,13 +9974,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>0</v>
       </c>
       <c r="S90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T90" s="10" t="n">
         <v>1</v>
@@ -10019,7 +10019,7 @@
         <v>1</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -14751,10 +14751,10 @@
         </is>
       </c>
       <c r="P136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R136" s="9" t="n">
         <v>0</v>
@@ -15413,7 +15413,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>

--- a/docs/d/116/inyear.xlsx
+++ b/docs/d/116/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 84 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 63 clubs short</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>57</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -992,8 +992,8 @@
       <c r="P3" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" s="9" t="n">
-        <v>1</v>
+      <c r="Q3" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R3" s="9" t="n">
         <v>0</v>
@@ -1007,11 +1007,11 @@
       <c r="U3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V3" s="9" t="n">
+      <c r="V3" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W3" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="W3" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X3" s="10" t="n">
         <v>6</v>
@@ -1278,13 +1278,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>2</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="9" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>4</v>
       </c>
       <c r="W6" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X6" s="10" t="n">
         <v>7</v>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="P10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="9" t="n">
         <v>0</v>
@@ -1750,8 +1750,8 @@
       <c r="Y10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>0</v>
+      <c r="Z10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" s="10" t="n">
         <v>1</v>
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>4</v>
       </c>
       <c r="W11" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X11" s="10" t="n">
         <v>4</v>
@@ -2096,7 +2096,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2110,13 +2110,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2154,11 +2154,11 @@
       <c r="U14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="9" t="n">
-        <v>3</v>
+      <c r="V14" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" s="10" t="n">
         <v>7</v>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2627,13 +2627,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="P19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="9" t="n">
         <v>0</v>
@@ -2663,22 +2663,22 @@
         <v>0</v>
       </c>
       <c r="S19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y19" s="9" t="n">
         <v>0</v>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="P20" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="X20" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20" s="9" t="n">
         <v>0</v>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2888,13 +2888,13 @@
         <v>0</v>
       </c>
       <c r="X21" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z21" s="9" t="n">
-        <v>0</v>
+      <c r="Z21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA21" s="10" t="n">
         <v>1</v>
@@ -2992,8 +2992,8 @@
       <c r="W22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X22" s="9" t="n">
-        <v>2</v>
+      <c r="X22" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y22" s="9" t="n">
         <v>0</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="P24" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="9" t="n">
         <v>0</v>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3923,8 +3923,8 @@
       <c r="Y31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z31" s="9" t="n">
-        <v>0</v>
+      <c r="Z31" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA31" s="10" t="n">
         <v>1</v>
@@ -4261,7 +4261,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4331,8 +4331,8 @@
       <c r="Y35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" s="9" t="n">
-        <v>0</v>
+      <c r="Z35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA35" s="10" t="n">
         <v>1</v>
@@ -4568,7 +4568,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4582,13 +4582,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4626,11 +4626,11 @@
       <c r="U38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V38" s="9" t="n">
-        <v>1</v>
+      <c r="V38" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X38" s="10" t="n">
         <v>6</v>
@@ -4673,7 +4673,7 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="P39" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>0</v>
@@ -4725,8 +4725,8 @@
       <c r="S39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T39" s="9" t="n">
-        <v>0</v>
+      <c r="T39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U39" s="9" t="n">
         <v>0</v>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4830,8 +4830,8 @@
       <c r="S40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T40" s="9" t="n">
-        <v>0</v>
+      <c r="T40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U40" s="9" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q48" s="9" t="n">
         <v>0</v>
@@ -5695,7 +5695,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5765,8 +5765,8 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="9" t="n">
-        <v>0</v>
+      <c r="Z49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5814,13 +5814,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5858,11 +5858,11 @@
       <c r="U50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V50" s="9" t="n">
-        <v>3</v>
+      <c r="V50" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X50" s="10" t="n">
         <v>6</v>
@@ -5975,8 +5975,8 @@
       <c r="Y51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="n">
-        <v>0</v>
+      <c r="Z51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="9" t="n">
         <v>0</v>
@@ -6418,7 +6418,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6488,8 +6488,8 @@
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="10" t="n">
         <v>1</v>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6563,8 +6563,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P57" s="9" t="n">
-        <v>3</v>
+      <c r="P57" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q57" s="9" t="n">
         <v>1</v>
@@ -6834,7 +6834,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6886,8 +6886,8 @@
       <c r="S60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T60" s="9" t="n">
-        <v>0</v>
+      <c r="T60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U60" s="9" t="n">
         <v>0</v>
@@ -6939,7 +6939,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6953,13 +6953,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -6997,11 +6997,11 @@
       <c r="U61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V61" s="9" t="n">
-        <v>1</v>
+      <c r="V61" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X61" s="10" t="n">
         <v>6</v>
@@ -7254,7 +7254,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7324,8 +7324,8 @@
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="9" t="n">
-        <v>0</v>
+      <c r="Z64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA64" s="10" t="n">
         <v>1</v>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7474,13 +7474,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
@@ -7518,11 +7518,11 @@
       <c r="U66" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V66" s="9" t="n">
-        <v>3</v>
+      <c r="V66" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X66" s="10" t="n">
         <v>7</v>
@@ -8247,7 +8247,7 @@
         <v>1</v>
       </c>
       <c r="U73" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V73" s="9" t="n">
         <v>2</v>
@@ -8712,7 +8712,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8782,8 +8782,8 @@
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -8827,13 +8827,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>0</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -9128,7 +9128,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9198,8 +9198,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -9338,7 +9338,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9390,8 +9390,8 @@
       <c r="S84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T84" s="9" t="n">
-        <v>0</v>
+      <c r="T84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U84" s="9" t="n">
         <v>0</v>
@@ -9408,8 +9408,8 @@
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="9" t="n">
-        <v>0</v>
+      <c r="Z84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
@@ -10170,7 +10170,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10184,13 +10184,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
@@ -10228,11 +10228,11 @@
       <c r="U92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V92" s="9" t="n">
-        <v>0</v>
+      <c r="V92" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X92" s="10" t="n">
         <v>7</v>
@@ -10275,7 +10275,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10345,8 +10345,8 @@
       <c r="Y93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" s="9" t="n">
-        <v>0</v>
+      <c r="Z93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA93" s="10" t="n">
         <v>1</v>
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
@@ -10446,8 +10446,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="10" t="n">
         <v>1</v>
@@ -10810,13 +10810,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>0</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11146,8 +11146,8 @@
       <c r="P101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" s="9" t="n">
-        <v>0</v>
+      <c r="Q101" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R101" s="9" t="n">
         <v>0</v>
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11274,8 +11274,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -11379,8 +11379,8 @@
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="9" t="n">
-        <v>0</v>
+      <c r="Z103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="9" t="n">
         <v>0</v>
@@ -11630,13 +11630,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -12246,7 +12246,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12316,8 +12316,8 @@
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -12516,8 +12516,8 @@
       <c r="W114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X114" s="9" t="n">
-        <v>0</v>
+      <c r="X114" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y114" s="9" t="n">
         <v>0</v>
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12627,8 +12627,8 @@
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -12763,7 +12763,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12833,8 +12833,8 @@
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="9" t="n">
-        <v>0</v>
+      <c r="Z117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -13034,7 +13034,7 @@
         <v>0</v>
       </c>
       <c r="X119" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
@@ -13272,7 +13272,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13342,8 +13342,8 @@
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13492,17 +13492,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M124" s="8" t="n">
@@ -13536,11 +13536,11 @@
       <c r="U124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V124" s="9" t="n">
-        <v>0</v>
+      <c r="V124" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X124" s="10" t="n">
         <v>4</v>
@@ -13548,8 +13548,8 @@
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA124" s="9" t="n">
         <v>0</v>
@@ -13579,7 +13579,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13593,13 +13593,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
@@ -13637,11 +13637,11 @@
       <c r="U125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V125" s="9" t="n">
-        <v>2</v>
+      <c r="V125" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X125" s="10" t="n">
         <v>7</v>
@@ -14267,8 +14267,8 @@
       <c r="Y131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="9" t="n">
-        <v>0</v>
+      <c r="Z131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA131" s="9" t="n">
         <v>0</v>
@@ -14518,13 +14518,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>2</v>
       </c>
       <c r="Q134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R134" s="9" t="n">
         <v>0</v>
@@ -14563,7 +14563,7 @@
         <v>0</v>
       </c>
       <c r="V134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14967,8 +14967,8 @@
       <c r="T138" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U138" s="9" t="n">
-        <v>0</v>
+      <c r="U138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V138" s="9" t="n">
         <v>0</v>
@@ -15182,13 +15182,13 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -15248,7 +15248,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -15314,7 +15314,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -15380,7 +15380,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -15413,7 +15413,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -15446,7 +15446,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -15479,7 +15479,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15545,7 +15545,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -15578,7 +15578,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -15611,7 +15611,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -15644,7 +15644,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -15677,7 +15677,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15743,7 +15743,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -15776,7 +15776,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15809,7 +15809,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -15875,7 +15875,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15941,7 +15941,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -16007,7 +16007,7 @@
         <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -16040,7 +16040,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -16073,7 +16073,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -16106,7 +16106,7 @@
         <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -16121,7 +16121,7 @@
         <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -16205,7 +16205,7 @@
         <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>

--- a/docs/d/116/inyear.xlsx
+++ b/docs/d/116/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 63 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 63 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>57</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>6</v>
+        <v>-29</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -1068,17 +1068,17 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M4" s="8" t="n">
@@ -1173,17 +1173,17 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M5" s="8" t="n">
@@ -1218,7 +1218,7 @@
         <v>0</v>
       </c>
       <c r="V5" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1278,17 +1278,17 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M6" s="8" t="n">
@@ -1325,8 +1325,8 @@
       <c r="V6" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W6" s="9" t="n">
-        <v>2</v>
+      <c r="W6" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X6" s="10" t="n">
         <v>7</v>
@@ -1383,13 +1383,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1484,17 +1484,17 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M8" s="8" t="n">
@@ -1589,17 +1589,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M9" s="8" t="n">
@@ -1634,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1694,17 +1694,17 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M10" s="8" t="n">
@@ -1739,7 +1739,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1799,17 +1799,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M11" s="8" t="n">
@@ -1847,7 +1847,7 @@
         <v>4</v>
       </c>
       <c r="W11" s="10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X11" s="10" t="n">
         <v>4</v>
@@ -1904,17 +1904,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L12" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="8" t="n">
@@ -2009,13 +2009,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2110,13 +2110,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="P14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="9" t="n">
         <v>0</v>
@@ -2211,13 +2211,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2312,13 +2312,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="P16" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>0</v>
@@ -2356,11 +2356,11 @@
       <c r="U16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V16" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W16" s="9" t="n">
-        <v>0</v>
+      <c r="V16" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W16" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X16" s="10" t="n">
         <v>7</v>
@@ -2417,17 +2417,17 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M17" s="8" t="n">
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="9" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -2627,13 +2627,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2732,13 +2732,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -2837,13 +2837,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -2942,13 +2942,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -3047,13 +3047,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3148,13 +3148,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="V24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>0</v>
@@ -3253,17 +3253,17 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M25" s="8" t="n">
@@ -3280,7 +3280,7 @@
         </is>
       </c>
       <c r="P25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="9" t="n">
         <v>1</v>
@@ -3358,13 +3358,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3459,13 +3459,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>46</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -3497,14 +3497,14 @@
       <c r="S27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T27" s="9" t="n">
-        <v>0</v>
+      <c r="T27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3564,13 +3564,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3766,13 +3766,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -3867,13 +3867,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         </is>
       </c>
       <c r="P31" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q31" s="9" t="n">
         <v>1</v>
@@ -3912,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3968,13 +3968,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -4069,13 +4069,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -4174,13 +4174,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4275,17 +4275,17 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M35" s="8" t="n">
@@ -4380,17 +4380,17 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M36" s="8" t="n">
@@ -4481,17 +4481,17 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-22</v>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M37" s="8" t="n">
@@ -4582,13 +4582,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4687,17 +4687,17 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M39" s="8" t="n">
@@ -4792,13 +4792,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4893,13 +4893,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4994,13 +4994,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -5095,17 +5095,17 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L43" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M43" s="8" t="n">
@@ -5297,13 +5297,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5398,17 +5398,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M46" s="8" t="n">
@@ -5443,7 +5443,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5503,13 +5503,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5604,17 +5604,17 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M48" s="8" t="n">
@@ -5709,17 +5709,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M49" s="8" t="n">
@@ -5814,13 +5814,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>4</v>
       </c>
       <c r="W50" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X50" s="10" t="n">
         <v>6</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5919,13 +5919,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5963,11 +5963,11 @@
       <c r="U51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V51" s="9" t="n">
-        <v>0</v>
+      <c r="V51" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X51" s="9" t="n">
         <v>0</v>
@@ -6020,13 +6020,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -6125,17 +6125,17 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-24</v>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M53" s="8" t="n">
@@ -6226,17 +6226,17 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M54" s="8" t="n">
@@ -6327,13 +6327,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6432,17 +6432,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="8" t="n">
@@ -6480,7 +6480,7 @@
         <v>4</v>
       </c>
       <c r="W56" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X56" s="10" t="n">
         <v>6</v>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6537,13 +6537,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>2</v>
+        <v>-14</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>0</v>
       </c>
       <c r="S57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" s="10" t="n">
         <v>1</v>
@@ -6581,11 +6581,11 @@
       <c r="U57" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V57" s="9" t="n">
-        <v>2</v>
+      <c r="V57" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>7</v>
@@ -6642,17 +6642,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-19</v>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M58" s="8" t="n">
@@ -6747,17 +6747,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-21</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M59" s="8" t="n">
@@ -6834,7 +6834,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6848,13 +6848,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
@@ -6895,8 +6895,8 @@
       <c r="V60" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W60" s="9" t="n">
-        <v>3</v>
+      <c r="W60" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>7</v>
@@ -6953,13 +6953,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
@@ -7058,17 +7058,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-18</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="8" t="n">
@@ -7103,7 +7103,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -7163,13 +7163,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7268,13 +7268,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7369,17 +7369,17 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M65" s="8" t="n">
@@ -7474,13 +7474,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
@@ -7579,17 +7579,17 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-17</v>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M67" s="8" t="n">
@@ -7670,7 +7670,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7684,17 +7684,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M68" s="8" t="n">
@@ -7731,8 +7731,8 @@
       <c r="V68" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W68" s="9" t="n">
-        <v>3</v>
+      <c r="W68" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X68" s="10" t="n">
         <v>7</v>
@@ -7789,17 +7789,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-19</v>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M69" s="8" t="n">
@@ -7894,13 +7894,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7995,17 +7995,17 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-19</v>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M71" s="8" t="n">
@@ -8100,17 +8100,17 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M72" s="8" t="n">
@@ -8205,13 +8205,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -8411,17 +8411,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-26</v>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M75" s="8" t="n">
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="P76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q76" s="9" t="n">
         <v>1</v>
@@ -8560,8 +8560,8 @@
       <c r="U76" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V76" s="9" t="n">
-        <v>1</v>
+      <c r="V76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8621,17 +8621,17 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M77" s="8" t="n">
@@ -8666,7 +8666,7 @@
         <v>0</v>
       </c>
       <c r="V77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -8726,17 +8726,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M78" s="8" t="n">
@@ -8827,13 +8827,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -8932,17 +8932,17 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L80" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M80" s="8" t="n">
@@ -9037,17 +9037,17 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M81" s="8" t="n">
@@ -9067,7 +9067,7 @@
         <v>3</v>
       </c>
       <c r="Q81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R81" s="9" t="n">
         <v>0</v>
@@ -9142,17 +9142,17 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M82" s="8" t="n">
@@ -9233,7 +9233,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -9247,13 +9247,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
@@ -9291,11 +9291,11 @@
       <c r="U83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V83" s="9" t="n">
-        <v>1</v>
+      <c r="V83" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W83" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X83" s="10" t="n">
         <v>7</v>
@@ -9352,13 +9352,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9457,17 +9457,17 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M85" s="8" t="n">
@@ -9501,8 +9501,8 @@
       <c r="U85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V85" s="9" t="n">
-        <v>2</v>
+      <c r="V85" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9562,13 +9562,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9663,17 +9663,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L87" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M87" s="8" t="n">
@@ -9768,13 +9768,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -9873,17 +9873,17 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L89" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M89" s="8" t="n">
@@ -9921,7 +9921,7 @@
         <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>7</v>
@@ -9960,7 +9960,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9974,13 +9974,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -10018,8 +10018,8 @@
       <c r="U90" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V90" s="9" t="n">
-        <v>3</v>
+      <c r="V90" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -10065,7 +10065,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10079,17 +10079,17 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L91" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M91" s="8" t="n">
@@ -10114,8 +10114,8 @@
       <c r="R91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S91" s="9" t="n">
-        <v>1</v>
+      <c r="S91" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T91" s="9" t="n">
         <v>0</v>
@@ -10184,13 +10184,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>44</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>5</v>
+        <v>-14</v>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>4</v>
       </c>
       <c r="W92" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X92" s="10" t="n">
         <v>7</v>
@@ -10289,13 +10289,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10495,17 +10495,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-25</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M95" s="8" t="n">
@@ -10600,13 +10600,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>1</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10705,17 +10705,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-23</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M97" s="8" t="n">
@@ -10810,17 +10810,17 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M98" s="8" t="n">
@@ -10915,13 +10915,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -11016,13 +11016,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         </is>
       </c>
       <c r="P100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q100" s="9" t="n">
         <v>0</v>
@@ -11061,7 +11061,7 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -11117,13 +11117,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -11218,17 +11218,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M102" s="8" t="n">
@@ -11263,7 +11263,7 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11323,17 +11323,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M103" s="8" t="n">
@@ -11367,11 +11367,11 @@
       <c r="U103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V103" s="9" t="n">
-        <v>0</v>
+      <c r="V103" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X103" s="10" t="n">
         <v>5</v>
@@ -11424,17 +11424,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M104" s="8" t="n">
@@ -11529,13 +11529,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-15</v>
+        <v>-18</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -11616,7 +11616,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11674,8 +11674,8 @@
       <c r="U106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V106" s="9" t="n">
-        <v>1</v>
+      <c r="V106" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -11735,17 +11735,17 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M107" s="8" t="n">
@@ -11780,7 +11780,7 @@
         <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -11840,17 +11840,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L108" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11945,17 +11945,17 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L109" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M109" s="8" t="n">
@@ -12050,13 +12050,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>4</v>
       </c>
       <c r="W110" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X110" s="10" t="n">
         <v>7</v>
@@ -12155,13 +12155,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>2</v>
       </c>
       <c r="R111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S111" s="9" t="n">
         <v>1</v>
@@ -12260,17 +12260,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L112" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M112" s="8" t="n">
@@ -12365,13 +12365,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12466,17 +12466,17 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L114" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M114" s="8" t="n">
@@ -12571,13 +12571,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>1</v>
+        <v>-23</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -12676,13 +12676,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12777,17 +12777,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L117" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M117" s="8" t="n">
@@ -12882,13 +12882,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12983,17 +12983,17 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-23</v>
+      </c>
+      <c r="L119" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M119" s="8" t="n">
@@ -13084,13 +13084,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -13185,13 +13185,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -13286,13 +13286,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13391,13 +13391,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13492,17 +13492,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L124" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M124" s="8" t="n">
@@ -13593,17 +13593,17 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L125" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M125" s="8" t="n">
@@ -13698,17 +13698,17 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-23</v>
+      </c>
+      <c r="L126" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M126" s="8" t="n">
@@ -13799,17 +13799,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-23</v>
+      </c>
+      <c r="L127" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M127" s="8" t="n">
@@ -13900,13 +13900,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -14001,17 +14001,17 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-18</v>
+      </c>
+      <c r="L129" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M129" s="8" t="n">
@@ -14106,17 +14106,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-25</v>
+      </c>
+      <c r="L130" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M130" s="8" t="n">
@@ -14211,13 +14211,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -14413,17 +14413,17 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M133" s="8" t="n">
@@ -14440,7 +14440,7 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q133" s="9" t="n">
         <v>0</v>
@@ -14458,7 +14458,7 @@
         <v>0</v>
       </c>
       <c r="V133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W133" s="9" t="n">
         <v>0</v>
@@ -14518,17 +14518,17 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L134" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M134" s="8" t="n">
@@ -14623,13 +14623,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>-15</v>
+        <v>-18</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -14724,17 +14724,17 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-19</v>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M136" s="8" t="n">
@@ -14825,13 +14825,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14926,17 +14926,17 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L138" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-24</v>
+      </c>
+      <c r="L138" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M138" s="8" t="n">
@@ -15027,13 +15027,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -15215,7 +15215,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15230,7 +15230,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -15263,7 +15263,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -15281,7 +15281,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15296,7 +15296,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -15362,7 +15362,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -15380,7 +15380,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -15428,7 +15428,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -15461,7 +15461,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -15494,7 +15494,7 @@
         <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -15527,7 +15527,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -15545,7 +15545,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -15560,7 +15560,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -15578,13 +15578,13 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -15593,7 +15593,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -15611,13 +15611,13 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -15626,7 +15626,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -15659,7 +15659,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -15677,7 +15677,7 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15692,7 +15692,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -15725,7 +15725,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -15743,7 +15743,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -15758,7 +15758,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -15791,7 +15791,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -15809,7 +15809,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -15824,7 +15824,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -15842,7 +15842,7 @@
         <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15875,7 +15875,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15890,7 +15890,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -15923,7 +15923,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -15941,7 +15941,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -15956,7 +15956,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -15974,7 +15974,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -15989,7 +15989,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -16022,7 +16022,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -16055,7 +16055,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -16088,7 +16088,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -16121,7 +16121,7 @@
         <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -16154,7 +16154,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -16187,7 +16187,7 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -16220,7 +16220,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/116/inyear.xlsx
+++ b/docs/d/116/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/116/inyear.xlsx
+++ b/docs/d/116/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/116/inyear.xlsx
+++ b/docs/d/116/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/116/inyear.xlsx
+++ b/docs/d/116/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/116/inyear.xlsx
+++ b/docs/d/116/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 63 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 63 clubs short</t>
         </is>
       </c>
     </row>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>57</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-29</v>
+        <v>-28</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
@@ -1217,8 +1217,8 @@
       <c r="U5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="9" t="n">
-        <v>3</v>
+      <c r="V5" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W5" s="9" t="n">
         <v>0</v>
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -2110,13 +2110,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2560,8 +2560,8 @@
       <c r="S18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T18" s="9" t="n">
-        <v>0</v>
+      <c r="T18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U18" s="9" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2770,8 +2770,8 @@
       <c r="S20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T20" s="9" t="n">
-        <v>0</v>
+      <c r="T20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U20" s="9" t="n">
         <v>0</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3488,8 +3488,8 @@
       <c r="P27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" s="9" t="n">
-        <v>1</v>
+      <c r="Q27" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R27" s="9" t="n">
         <v>0</v>
@@ -4174,13 +4174,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
@@ -4687,13 +4687,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -5604,13 +5604,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6537,13 +6537,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         </is>
       </c>
       <c r="P57" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q57" s="9" t="n">
         <v>1</v>
@@ -6572,8 +6572,8 @@
       <c r="R57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S57" s="9" t="n">
-        <v>1</v>
+      <c r="S57" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T57" s="10" t="n">
         <v>1</v>
@@ -6584,8 +6584,8 @@
       <c r="V57" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W57" s="9" t="n">
-        <v>3</v>
+      <c r="W57" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>7</v>
@@ -6848,13 +6848,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>4</v>
       </c>
       <c r="W60" s="10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>7</v>
@@ -7504,7 +7504,7 @@
         <v>1</v>
       </c>
       <c r="Q66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" s="9" t="n">
         <v>0</v>
@@ -7684,13 +7684,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="P68" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q68" s="9" t="n">
         <v>0</v>
@@ -7732,7 +7732,7 @@
         <v>4</v>
       </c>
       <c r="W68" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X68" s="10" t="n">
         <v>7</v>
@@ -7789,13 +7789,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="P73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q73" s="9" t="n">
         <v>0</v>
@@ -8241,13 +8241,13 @@
         <v>0</v>
       </c>
       <c r="S73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U73" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V73" s="9" t="n">
         <v>2</v>
@@ -8411,13 +8411,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-26</v>
+        <v>-25</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>0</v>
       </c>
       <c r="V77" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -9457,13 +9457,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9768,13 +9768,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>0</v>
       </c>
       <c r="Q88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" s="9" t="n">
         <v>0</v>
@@ -9813,7 +9813,7 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
@@ -11323,13 +11323,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>4</v>
       </c>
       <c r="W103" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X103" s="10" t="n">
         <v>5</v>
@@ -11529,13 +11529,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-18</v>
+        <v>-17</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -11735,13 +11735,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11840,13 +11840,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -12260,13 +12260,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14547,8 +14547,8 @@
       <c r="P134" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q134" s="9" t="n">
-        <v>1</v>
+      <c r="Q134" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R134" s="9" t="n">
         <v>0</v>
@@ -15182,7 +15182,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -15281,7 +15281,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15314,7 +15314,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -15380,7 +15380,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -15578,7 +15578,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -16172,7 +16172,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>

--- a/docs/d/116/inyear.xlsx
+++ b/docs/d/116/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 63 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 63 clubs short</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="P3" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q3" s="10" t="n">
         <v>2</v>
@@ -999,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T3" s="10" t="n">
         <v>1</v>
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="P14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" s="9" t="n">
         <v>0</v>
@@ -4174,13 +4174,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4380,13 +4380,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>-17</v>
+        <v>-7</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c r="P43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q43" s="9" t="n">
         <v>0</v>
@@ -6327,13 +6327,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6642,13 +6642,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6848,13 +6848,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>4</v>
       </c>
       <c r="W60" s="10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X60" s="10" t="n">
         <v>7</v>
@@ -7163,13 +7163,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>4</v>
       </c>
       <c r="W63" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X63" s="10" t="n">
         <v>7</v>
@@ -8558,7 +8558,7 @@
         <v>1</v>
       </c>
       <c r="U76" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V76" s="10" t="n">
         <v>4</v>
@@ -9457,13 +9457,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>4</v>
       </c>
       <c r="W85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X85" s="10" t="n">
         <v>7</v>
@@ -10115,7 +10115,7 @@
         <v>0</v>
       </c>
       <c r="S91" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T91" s="9" t="n">
         <v>0</v>
@@ -10796,7 +10796,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10848,8 +10848,8 @@
       <c r="S98" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T98" s="9" t="n">
-        <v>0</v>
+      <c r="T98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U98" s="9" t="n">
         <v>0</v>
@@ -11735,13 +11735,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -12571,13 +12571,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>-23</v>
+        <v>-19</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>0</v>
       </c>
       <c r="V126" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
@@ -14399,7 +14399,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14454,8 +14454,8 @@
       <c r="T133" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U133" s="9" t="n">
-        <v>0</v>
+      <c r="U133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V133" s="9" t="n">
         <v>1</v>
@@ -14518,13 +14518,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -15908,7 +15908,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -16172,7 +16172,7 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
